--- a/artfynd/A 27364-2023 artfynd.xlsx
+++ b/artfynd/A 27364-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27364-2023 artfynd.xlsx
+++ b/artfynd/A 27364-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56145400</v>
+        <v>103995198</v>
       </c>
       <c r="B2" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>389</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548975.3224483917</v>
+        <v>549074</v>
       </c>
       <c r="R2" t="n">
-        <v>7088697.637742624</v>
+        <v>7088505</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-05-22</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-05-22</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,47 +767,34 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>granskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # högstubbe</t>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niina Sallmén, Ulrika Westling</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103995198</v>
+        <v>104023361</v>
       </c>
       <c r="B3" t="n">
-        <v>78477</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549073.9698253343</v>
+        <v>549077</v>
       </c>
       <c r="R3" t="n">
-        <v>7088505.091294833</v>
+        <v>7088494</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,11 +882,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -925,15 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103995199</v>
+        <v>56145400</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549068.0706087084</v>
+        <v>548975</v>
       </c>
       <c r="R4" t="n">
-        <v>7088487.833562615</v>
+        <v>7088698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,22 +967,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>08:11</t>
+          <t>2015-05-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>08:11</t>
+          <t>2015-05-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,61 +984,64 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter # högstubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Niina Sallmén, Ulrika Westling</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104023361</v>
+        <v>104023360</v>
       </c>
       <c r="B5" t="n">
-        <v>78477</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>389</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549077.2265661653</v>
+        <v>549105</v>
       </c>
       <c r="R5" t="n">
-        <v>7088494.139053114</v>
+        <v>7088465</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,16 +1130,11 @@
         <v>104023362</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1202,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549097.7827879555</v>
+        <v>549098</v>
       </c>
       <c r="R6" t="n">
-        <v>7088504.144505456</v>
+        <v>7088504</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1281,12 +1241,7 @@
         <v>104023363</v>
       </c>
       <c r="B7" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549089.8658443992</v>
+        <v>549090</v>
       </c>
       <c r="R7" t="n">
-        <v>7088503.140009173</v>
+        <v>7088503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1394,37 +1349,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104023360</v>
+        <v>103995199</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1434,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549105.4470105463</v>
+        <v>549068</v>
       </c>
       <c r="R8" t="n">
-        <v>7088465.092747113</v>
+        <v>7088488</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,6 +1440,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 27364-2023 artfynd.xlsx
+++ b/artfynd/A 27364-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995198</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023361</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56145400</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023360</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023362</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023363</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1462,8 +1497,22 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995199</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>